--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BAUHAUS GODELLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BAUHAUS GODELLA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. CASADO SEGURA</t>
+          <t>P. FERRI BARCENAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>30.2591</v>
+        <v>27.5953</v>
       </c>
       <c r="E2" t="n">
-        <v>26.7416</v>
+        <v>16.1893</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5178</v>
+        <v>11.4065</v>
       </c>
       <c r="G2" t="n">
-        <v>21.6672</v>
+        <v>7.1845</v>
       </c>
       <c r="H2" t="n">
-        <v>17.3489</v>
+        <v>10.8183</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3185</v>
+        <v>-3.6335</v>
       </c>
       <c r="J2" t="n">
-        <v>38.2312</v>
+        <v>24.0968</v>
       </c>
       <c r="K2" t="n">
-        <v>34.9655</v>
+        <v>24.2645</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2656</v>
+        <v>-0.1675000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-16.5642</v>
+        <v>-16.9123</v>
       </c>
       <c r="N2" t="n">
-        <v>-17.6165</v>
+        <v>-13.4463</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0525</v>
+        <v>-3.4658</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2826</v>
+        <v>-0.1830999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-36.2852</v>
+        <v>-35.552</v>
       </c>
       <c r="R2" t="n">
-        <v>37.5676</v>
+        <v>35.3686</v>
       </c>
       <c r="S2" t="n">
-        <v>6.185499999999999</v>
+        <v>0.3872000000000002</v>
       </c>
       <c r="T2" t="n">
-        <v>11.6994</v>
+        <v>-0.3538999999999998</v>
       </c>
       <c r="U2" t="n">
-        <v>-5.5138</v>
+        <v>0.741</v>
       </c>
       <c r="V2" t="n">
-        <v>1.123700000000001</v>
+        <v>20.2071</v>
       </c>
       <c r="W2" t="n">
-        <v>13.0959</v>
+        <v>27.9981</v>
       </c>
       <c r="X2" t="n">
-        <v>-11.972</v>
+        <v>-7.7911</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. FERRI BARCENAS</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>19.474</v>
+        <v>27.3266</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8194</v>
+        <v>7.638200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>7.6542</v>
+        <v>19.6883</v>
       </c>
       <c r="G3" t="n">
-        <v>7.1845</v>
+        <v>20.2399</v>
       </c>
       <c r="H3" t="n">
-        <v>10.8183</v>
+        <v>2.369899999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.6335</v>
+        <v>17.8698</v>
       </c>
       <c r="J3" t="n">
-        <v>24.0968</v>
+        <v>33.253</v>
       </c>
       <c r="K3" t="n">
-        <v>24.2645</v>
+        <v>17.1722</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1675000000000001</v>
+        <v>16.0809</v>
       </c>
       <c r="M3" t="n">
-        <v>-16.9123</v>
+        <v>-13.0134</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.4463</v>
+        <v>-14.8023</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.4658</v>
+        <v>1.7889</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1830999999999999</v>
+        <v>-2.5657</v>
       </c>
       <c r="Q3" t="n">
-        <v>-35.552</v>
+        <v>-46.5475</v>
       </c>
       <c r="R3" t="n">
-        <v>35.3686</v>
+        <v>43.982</v>
       </c>
       <c r="S3" t="n">
-        <v>-7.7344</v>
+        <v>2.354</v>
       </c>
       <c r="T3" t="n">
-        <v>-4.7235</v>
+        <v>-0.7205999999999998</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.0107</v>
+        <v>3.0748</v>
       </c>
       <c r="V3" t="n">
-        <v>20.2071</v>
+        <v>7.2985</v>
       </c>
       <c r="W3" t="n">
-        <v>27.9981</v>
+        <v>21.6528</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.7911</v>
+        <v>-14.3543</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>17.9902</v>
+        <v>26.6295</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.4053</v>
+        <v>35.8254</v>
       </c>
       <c r="F4" t="n">
-        <v>20.395</v>
+        <v>-9.1959</v>
       </c>
       <c r="G4" t="n">
-        <v>20.2399</v>
+        <v>26.343</v>
       </c>
       <c r="H4" t="n">
-        <v>2.369899999999999</v>
+        <v>-9.5464</v>
       </c>
       <c r="I4" t="n">
-        <v>17.8698</v>
+        <v>35.889</v>
       </c>
       <c r="J4" t="n">
-        <v>33.253</v>
+        <v>49.6335</v>
       </c>
       <c r="K4" t="n">
-        <v>17.1722</v>
+        <v>14.4447</v>
       </c>
       <c r="L4" t="n">
-        <v>16.0809</v>
+        <v>35.189</v>
       </c>
       <c r="M4" t="n">
-        <v>-13.0134</v>
+        <v>-23.2906</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.8023</v>
+        <v>-23.9906</v>
       </c>
       <c r="O4" t="n">
-        <v>1.7889</v>
+        <v>0.7002</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.5657</v>
+        <v>-5.680999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-46.5475</v>
+        <v>-42.3327</v>
       </c>
       <c r="R4" t="n">
-        <v>43.982</v>
+        <v>36.6516</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.9824</v>
+        <v>-3.9147</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.7641</v>
+        <v>-1.9869</v>
       </c>
       <c r="U4" t="n">
-        <v>3.7818</v>
+        <v>-1.9278</v>
       </c>
       <c r="V4" t="n">
-        <v>7.2985</v>
+        <v>9.8826</v>
       </c>
       <c r="W4" t="n">
-        <v>21.6528</v>
+        <v>30.5113</v>
       </c>
       <c r="X4" t="n">
-        <v>-14.3543</v>
+        <v>-20.6287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>J. CASADO SEGURA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>13.77</v>
+        <v>26.1564</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.588699999999999</v>
+        <v>19.4083</v>
       </c>
       <c r="F5" t="n">
-        <v>18.3585</v>
+        <v>6.7483</v>
       </c>
       <c r="G5" t="n">
-        <v>-13.3908</v>
+        <v>21.6672</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.1617</v>
+        <v>17.3489</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.229</v>
+        <v>4.3185</v>
       </c>
       <c r="J5" t="n">
-        <v>8.597100000000001</v>
+        <v>38.2312</v>
       </c>
       <c r="K5" t="n">
-        <v>10.4869</v>
+        <v>34.9655</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.89</v>
+        <v>3.2656</v>
       </c>
       <c r="M5" t="n">
-        <v>-21.988</v>
+        <v>-16.5642</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.6487</v>
+        <v>-17.6165</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3395</v>
+        <v>1.0525</v>
       </c>
       <c r="P5" t="n">
-        <v>-9.712399999999999</v>
+        <v>1.2826</v>
       </c>
       <c r="Q5" t="n">
-        <v>-50.7624</v>
+        <v>-36.2852</v>
       </c>
       <c r="R5" t="n">
-        <v>41.0497</v>
+        <v>37.5676</v>
       </c>
       <c r="S5" t="n">
-        <v>32.1127</v>
+        <v>2.0827</v>
       </c>
       <c r="T5" t="n">
-        <v>12.9943</v>
+        <v>4.366000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>19.118</v>
+        <v>-2.2834</v>
       </c>
       <c r="V5" t="n">
-        <v>4.760400000000001</v>
+        <v>1.123700000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>24.5817</v>
+        <v>13.0959</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.821</v>
+        <v>-11.972</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>T. ROIG ARIÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>12.0554</v>
+        <v>10.9029</v>
       </c>
       <c r="E6" t="n">
-        <v>11.2237</v>
+        <v>10.9029</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8317000000000003</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>11.59</v>
+        <v>10.9029</v>
       </c>
       <c r="H6" t="n">
-        <v>3.162</v>
+        <v>7.1523</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4284</v>
+        <v>3.7506</v>
       </c>
       <c r="J6" t="n">
-        <v>11.9558</v>
+        <v>10.9029</v>
       </c>
       <c r="K6" t="n">
-        <v>8.685600000000001</v>
+        <v>7.1523</v>
       </c>
       <c r="L6" t="n">
-        <v>3.27</v>
+        <v>3.7506</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3660999999999999</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.5237</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5.157900000000001</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>11.545</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-9.529500000000001</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>21.0744</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7679</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>5.286799999999999</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5191000000000002</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-15.8477</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5101</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-19.3578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. ROIG ARIÑO</t>
+          <t>J. SÁEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,34 +952,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>10.9029</v>
+        <v>10.4523</v>
       </c>
       <c r="E7" t="n">
-        <v>10.9029</v>
+        <v>10.4523</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10.9029</v>
+        <v>10.4523</v>
       </c>
       <c r="H7" t="n">
-        <v>7.1523</v>
+        <v>3.5761</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7506</v>
+        <v>6.8761</v>
       </c>
       <c r="J7" t="n">
-        <v>10.9029</v>
+        <v>10.4523</v>
       </c>
       <c r="K7" t="n">
-        <v>7.1523</v>
+        <v>3.5761</v>
       </c>
       <c r="L7" t="n">
-        <v>3.7506</v>
+        <v>6.8761</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SÁEZ GONZÁLEZ</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>10.4523</v>
+        <v>7.943599999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>10.4523</v>
+        <v>6.829400000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.1147</v>
       </c>
       <c r="G8" t="n">
-        <v>10.4523</v>
+        <v>11.59</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5761</v>
+        <v>3.162</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8761</v>
+        <v>8.4284</v>
       </c>
       <c r="J8" t="n">
-        <v>10.4523</v>
+        <v>11.9558</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5761</v>
+        <v>8.685600000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>6.8761</v>
+        <v>3.27</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.3660999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-5.5237</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.157900000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11.545</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-9.529500000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>21.0744</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.6564</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.8924000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.2362</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-15.8477</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.5101</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-19.3578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>10.0188</v>
+        <v>7.3429</v>
       </c>
       <c r="E9" t="n">
-        <v>24.8203</v>
+        <v>5.172899999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-14.8014</v>
+        <v>2.1698</v>
       </c>
       <c r="G9" t="n">
-        <v>26.343</v>
+        <v>5.0143</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.5464</v>
+        <v>-1.9151</v>
       </c>
       <c r="I9" t="n">
-        <v>35.889</v>
+        <v>6.9294</v>
       </c>
       <c r="J9" t="n">
-        <v>49.6335</v>
+        <v>8.889200000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>14.4447</v>
+        <v>5.7083</v>
       </c>
       <c r="L9" t="n">
-        <v>35.189</v>
+        <v>3.1808</v>
       </c>
       <c r="M9" t="n">
-        <v>-23.2906</v>
+        <v>-3.8748</v>
       </c>
       <c r="N9" t="n">
-        <v>-23.9906</v>
+        <v>-7.6234</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7002</v>
+        <v>3.7487</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.680999999999999</v>
+        <v>3.2986</v>
       </c>
       <c r="Q9" t="n">
-        <v>-42.3327</v>
+        <v>-10.4459</v>
       </c>
       <c r="R9" t="n">
-        <v>36.6516</v>
+        <v>13.7445</v>
       </c>
       <c r="S9" t="n">
-        <v>-20.5254</v>
+        <v>3.427</v>
       </c>
       <c r="T9" t="n">
-        <v>-12.9919</v>
+        <v>1.3187</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.5335</v>
+        <v>2.1082</v>
       </c>
       <c r="V9" t="n">
-        <v>9.8826</v>
+        <v>-4.3972</v>
       </c>
       <c r="W9" t="n">
-        <v>30.5113</v>
+        <v>5.4105</v>
       </c>
       <c r="X9" t="n">
-        <v>-20.6287</v>
+        <v>-9.807700000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6.810599999999999</v>
+        <v>5.2987</v>
       </c>
       <c r="E10" t="n">
-        <v>6.3672</v>
+        <v>2.2694</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4432999999999996</v>
+        <v>3.0293</v>
       </c>
       <c r="G10" t="n">
-        <v>5.0143</v>
+        <v>5.7869</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9151</v>
+        <v>5.224600000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9294</v>
+        <v>0.5624000000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>8.889200000000001</v>
+        <v>6.1233</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7083</v>
+        <v>5.752800000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>3.1808</v>
+        <v>0.3704999999999998</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.8748</v>
+        <v>-0.3365</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.6234</v>
+        <v>-0.5283</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7487</v>
+        <v>0.1919000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2986</v>
+        <v>-0.5497</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.4459</v>
+        <v>-5.8643</v>
       </c>
       <c r="R10" t="n">
-        <v>13.7445</v>
+        <v>5.3144</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8945</v>
+        <v>1.0273</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5129</v>
+        <v>0.7433</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3813</v>
+        <v>0.2841</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.3972</v>
+        <v>-0.9658</v>
       </c>
       <c r="W10" t="n">
-        <v>5.4105</v>
+        <v>1.267</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.807700000000001</v>
+        <v>-2.2328</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>4.5496</v>
+        <v>4.4543</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3761</v>
+        <v>-6.707000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1735</v>
+        <v>11.1615</v>
       </c>
       <c r="G11" t="n">
-        <v>5.7869</v>
+        <v>-2.9597</v>
       </c>
       <c r="H11" t="n">
-        <v>5.224600000000001</v>
+        <v>-1.7574</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5624000000000002</v>
+        <v>-1.2024</v>
       </c>
       <c r="J11" t="n">
-        <v>6.1233</v>
+        <v>12.602</v>
       </c>
       <c r="K11" t="n">
-        <v>5.752800000000001</v>
+        <v>11.396</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3704999999999998</v>
+        <v>1.2063</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3365</v>
+        <v>-15.5614</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5283</v>
+        <v>-13.153</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1919000000000001</v>
+        <v>-2.4086</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5497</v>
+        <v>-6.230499999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.8643</v>
+        <v>-39.2171</v>
       </c>
       <c r="R11" t="n">
-        <v>5.3144</v>
+        <v>32.9865</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2783</v>
+        <v>-1.4197</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1501</v>
+        <v>-1.1012</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4283</v>
+        <v>-0.3186</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9658</v>
+        <v>15.0644</v>
       </c>
       <c r="W11" t="n">
-        <v>1.267</v>
+        <v>21.009</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2328</v>
+        <v>-5.9444</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9339</v>
+        <v>4.3026</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7667</v>
+        <v>3.8628</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1673</v>
+        <v>0.4398</v>
       </c>
       <c r="G12" t="n">
         <v>1.7786</v>
@@ -1390,13 +1390,13 @@
         <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3945</v>
+        <v>-1.0258</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6056</v>
+        <v>-0.5094</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7889</v>
+        <v>-0.5164</v>
       </c>
       <c r="V12" t="n">
         <v>1.9005</v>
@@ -1423,13 +1423,13 @@
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>3.373499999999999</v>
+        <v>1.0161</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0431</v>
+        <v>1.8933</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3308</v>
+        <v>-0.8772</v>
       </c>
       <c r="G13" t="n">
         <v>1.3125</v>
@@ -1468,13 +1468,13 @@
         <v>15.0271</v>
       </c>
       <c r="S13" t="n">
-        <v>5.621</v>
+        <v>3.2632</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0906</v>
+        <v>1.9409</v>
       </c>
       <c r="U13" t="n">
-        <v>3.5301</v>
+        <v>1.3224</v>
       </c>
       <c r="V13" t="n">
         <v>-4.4761</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. CATALAN CALVO</t>
+          <t>P. PALOMARES MONZO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4221</v>
+        <v>-0.0298</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5504</v>
+        <v>-0.0468</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1283</v>
+        <v>0.017</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0547</v>
+        <v>0.3273</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3721</v>
+        <v>0.1895</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3175</v>
+        <v>0.1378</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7797</v>
+        <v>0.0633</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0712</v>
+        <v>0.0217</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7085</v>
+        <v>0.0417</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.725</v>
+        <v>0.264</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0.1679</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0259</v>
+        <v>0.0961</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9722</v>
+        <v>-0.5403</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9147999999999999</v>
+        <v>-0.1101</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0574</v>
+        <v>-0.4302</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. PALOMARES MONZO</t>
+          <t>A. BULDU IZQUIERDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1344</v>
+        <v>-0.1885</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1018</v>
+        <v>2.1825</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0326</v>
+        <v>-2.371</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3273</v>
+        <v>1.4852</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1895</v>
+        <v>1.3923</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1378</v>
+        <v>0.0929</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0633</v>
+        <v>3.1811</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0217</v>
+        <v>3.0561</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0417</v>
+        <v>0.125</v>
       </c>
       <c r="M15" t="n">
-        <v>0.264</v>
+        <v>-1.6959</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1679</v>
+        <v>-1.6638</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0961</v>
+        <v>-0.0321</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1833</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R15" t="n">
         <v>0.1833</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6449</v>
+        <v>0.6092</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1652</v>
+        <v>0.5121</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4798</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BULDU IZQUIERDO</t>
+          <t>F. CATALAN CALVO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4665</v>
+        <v>-0.3719</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1275</v>
+        <v>-0.2188</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.594</v>
+        <v>-0.1531</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4852</v>
+        <v>0.0547</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3923</v>
+        <v>0.3721</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0929</v>
+        <v>-0.3175</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1811</v>
+        <v>1.7797</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0561</v>
+        <v>1.0712</v>
       </c>
       <c r="L16" t="n">
-        <v>0.125</v>
+        <v>0.7085</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6959</v>
+        <v>-1.725</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6638</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0321</v>
+        <v>-1.0259</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6493</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1833</v>
+        <v>0.9163</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3312</v>
+        <v>0.1782</v>
       </c>
       <c r="T16" t="n">
-        <v>0.457</v>
+        <v>0.1456</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1259</v>
+        <v>0.0326</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6335</v>
+        <v>0.3115</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9554</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4735</v>
+        <v>-1.0043</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7634</v>
+        <v>-2.5711</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2899</v>
+        <v>1.5667</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3629</v>
@@ -1780,13 +1780,13 @@
         <v>0.5498</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3775</v>
+        <v>0.0916</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1573</v>
+        <v>0.1195</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>R. TORREGROSA ROCA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5248</v>
+        <v>-2.4376</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.656200000000001</v>
+        <v>-5.618300000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>6.131399999999999</v>
+        <v>3.1809</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9597</v>
+        <v>-6.0561</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7574</v>
+        <v>-0.2728000000000002</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2024</v>
+        <v>-5.7831</v>
       </c>
       <c r="J18" t="n">
-        <v>12.602</v>
+        <v>2.4942</v>
       </c>
       <c r="K18" t="n">
-        <v>11.396</v>
+        <v>6.9935</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2063</v>
+        <v>-4.4994</v>
       </c>
       <c r="M18" t="n">
-        <v>-15.5614</v>
+        <v>-8.5503</v>
       </c>
       <c r="N18" t="n">
-        <v>-13.153</v>
+        <v>-7.2664</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4086</v>
+        <v>-1.2839</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.230499999999999</v>
+        <v>2.5656</v>
       </c>
       <c r="Q18" t="n">
-        <v>-39.2171</v>
+        <v>-13.1947</v>
       </c>
       <c r="R18" t="n">
-        <v>32.9865</v>
+        <v>15.7601</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.398899999999999</v>
+        <v>2.4672</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.0501</v>
+        <v>1.9041</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.348800000000001</v>
+        <v>0.5631</v>
       </c>
       <c r="V18" t="n">
-        <v>15.0644</v>
+        <v>-1.4143</v>
       </c>
       <c r="W18" t="n">
-        <v>21.009</v>
+        <v>3.1778</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.9444</v>
+        <v>-4.5921</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SEGURA MORENO</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9755</v>
+        <v>-3.406699999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2455</v>
+        <v>-13.2542</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.73</v>
+        <v>9.8476</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9884</v>
+        <v>-13.3908</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.95</v>
+        <v>-8.1617</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0384</v>
+        <v>-5.229</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4069</v>
+        <v>8.597100000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1826</v>
+        <v>10.4869</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5895</v>
+        <v>-1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5815</v>
+        <v>-21.988</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1326</v>
+        <v>-18.6487</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4489</v>
+        <v>-3.3395</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3823</v>
+        <v>-9.712399999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6651</v>
+        <v>-50.7624</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2828</v>
+        <v>41.0497</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5498</v>
+        <v>14.936</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4404</v>
+        <v>4.3288</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1094</v>
+        <v>10.6072</v>
       </c>
       <c r="V19" t="n">
-        <v>0.945</v>
+        <v>4.760400000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>24.5817</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3219</v>
+        <v>-19.821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. TORREGROSA ROCA</t>
+          <t>J. SEGURA MORENO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.678100000000001</v>
+        <v>-3.5588</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.127800000000001</v>
+        <v>-2.957</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4494</v>
+        <v>-0.6018</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.0561</v>
+        <v>-1.9884</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2728000000000002</v>
+        <v>-0.95</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.7831</v>
+        <v>-1.0384</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4942</v>
+        <v>-0.4069</v>
       </c>
       <c r="K20" t="n">
-        <v>6.9935</v>
+        <v>0.1826</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.4994</v>
+        <v>-0.5895</v>
       </c>
       <c r="M20" t="n">
-        <v>-8.5503</v>
+        <v>-1.5815</v>
       </c>
       <c r="N20" t="n">
-        <v>-7.2664</v>
+        <v>-1.1326</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2839</v>
+        <v>-0.4489</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5656</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q20" t="n">
-        <v>-13.1947</v>
+        <v>-3.6651</v>
       </c>
       <c r="R20" t="n">
-        <v>15.7601</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2265999999999999</v>
+        <v>-0.1331</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3946</v>
+        <v>-0.152</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1678</v>
+        <v>0.0188</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4143</v>
+        <v>0.945</v>
       </c>
       <c r="W20" t="n">
-        <v>3.1778</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.5921</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.936599999999999</v>
+        <v>-3.6237</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.051299999999999</v>
+        <v>-5.581</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1149</v>
+        <v>1.9576</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8393</v>
@@ -2092,13 +2092,13 @@
         <v>5.8643</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.5967</v>
+        <v>-1.2839</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.7097</v>
+        <v>-0.2393</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8871</v>
+        <v>-1.0443</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3492</v>
@@ -2125,13 +2125,13 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.744999999999999</v>
+        <v>-9.1785</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.074</v>
+        <v>-7.581799999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6708</v>
+        <v>-1.5967</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3024</v>
@@ -2170,13 +2170,13 @@
         <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01260000000000006</v>
+        <v>-0.4210000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1245000000000001</v>
+        <v>-0.3835</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1119</v>
+        <v>-0.03749999999999995</v>
       </c>
       <c r="V22" t="n">
         <v>-3.8217</v>
@@ -2203,13 +2203,13 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.2501</v>
+        <v>-9.2713</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.8285</v>
+        <v>-8.047799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4216</v>
+        <v>-1.2234</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0631</v>
@@ -2248,13 +2248,13 @@
         <v>3.8484</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6936</v>
+        <v>-0.7150000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.04000000000000009</v>
+        <v>-0.2594</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6537000000000001</v>
+        <v>-0.4555</v>
       </c>
       <c r="V23" t="n">
         <v>-3.9277</v>
@@ -2281,13 +2281,13 @@
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.3944</v>
+        <v>-19.4775</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.0142</v>
+        <v>-11.0707</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.379899999999999</v>
+        <v>-8.4072</v>
       </c>
       <c r="G24" t="n">
         <v>-13.6388</v>
@@ -2326,13 +2326,13 @@
         <v>29.8709</v>
       </c>
       <c r="S24" t="n">
-        <v>1.113</v>
+        <v>1.0296</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7246</v>
+        <v>0.6683000000000002</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6114000000000002</v>
+        <v>0.3617</v>
       </c>
       <c r="V24" t="n">
         <v>-19.6964</v>
@@ -2359,13 +2359,13 @@
         <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.6476</v>
+        <v>-20.5919</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.826599999999999</v>
+        <v>-9.4168</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.821</v>
+        <v>-11.1752</v>
       </c>
       <c r="G25" t="n">
         <v>-18.6747</v>
@@ -2404,13 +2404,13 @@
         <v>9.7127</v>
       </c>
       <c r="S25" t="n">
-        <v>2.738599999999999</v>
+        <v>1.7943</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9369</v>
+        <v>2.3467</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1982</v>
+        <v>-0.5522999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-4.4449</v>
@@ -2437,13 +2437,13 @@
         <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>-32.3925</v>
+        <v>-22.9234</v>
       </c>
       <c r="E26" t="n">
-        <v>-25.6277</v>
+        <v>-20.2283</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.7647</v>
+        <v>-2.6949</v>
       </c>
       <c r="G26" t="n">
         <v>-5.2022</v>
@@ -2482,13 +2482,13 @@
         <v>18.8754</v>
       </c>
       <c r="S26" t="n">
-        <v>-15.0949</v>
+        <v>-5.6257</v>
       </c>
       <c r="T26" t="n">
-        <v>-8.1929</v>
+        <v>-2.7936</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.902</v>
+        <v>-2.8323</v>
       </c>
       <c r="V26" t="n">
         <v>-10.9955</v>
@@ -2515,13 +2515,13 @@
         <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>-39.5475</v>
+        <v>-37.1529</v>
       </c>
       <c r="E27" t="n">
-        <v>-38.227</v>
+        <v>-37.3876</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.32</v>
+        <v>0.2344000000000003</v>
       </c>
       <c r="G27" t="n">
         <v>-36.3805</v>
@@ -2560,13 +2560,13 @@
         <v>28.588</v>
       </c>
       <c r="S27" t="n">
-        <v>4.700100000000001</v>
+        <v>7.0945</v>
       </c>
       <c r="T27" t="n">
-        <v>4.5035</v>
+        <v>5.3431</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1965000000000003</v>
+        <v>1.7511</v>
       </c>
       <c r="V27" t="n">
         <v>-6.5842</v>
@@ -2593,22 +2593,22 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.154099999999985</v>
+        <v>26.20439999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-19.3468</v>
+        <v>-8.060499999999994</v>
       </c>
       <c r="F28" t="n">
-        <v>16.1934</v>
+        <v>34.26600000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>14.28040000000001</v>
+        <v>14.2804</v>
       </c>
       <c r="H28" t="n">
         <v>-22.2701</v>
       </c>
       <c r="I28" t="n">
-        <v>36.5508</v>
+        <v>36.55079999999998</v>
       </c>
       <c r="J28" t="n">
         <v>195.9121</v>
@@ -2638,16 +2638,16 @@
         <v>402.2501</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.038800000000004</v>
+        <v>26.3192</v>
       </c>
       <c r="T28" t="n">
-        <v>4.586199999999997</v>
+        <v>15.8722</v>
       </c>
       <c r="U28" t="n">
-        <v>-7.625900000000004</v>
+        <v>10.4471</v>
       </c>
       <c r="V28" t="n">
-        <v>-18.0605</v>
+        <v>-18.06049999999999</v>
       </c>
       <c r="W28" t="n">
         <v>178.7379</v>
